--- a/data/trans_orig/IP22D2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22D2_2023-Estudios-trans_orig.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>19068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>31836</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>13905</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23308</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26653</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>33090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47409</t>
+          <t>46846</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9306</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33880</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56130</t>
+          <t>54485</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>44136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64581</t>
+          <t>65998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22D2_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4099</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4583</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>27,54%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4911</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>17,17%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>81,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6174</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>58,62%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4969</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>18,67%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>60,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>66,26%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2929</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3692</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11857</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17854</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>35,18%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>52,97%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>11140</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7219</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>16306</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>36,87%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>21923</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31836</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20454</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14760</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25301</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>75,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19071</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13905</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22992</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>63,13%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21337</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26524</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>33690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46846</t>
+          <t>47402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -1515,107 +1515,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4186</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>5270</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5745</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2958</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2635</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2276</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2730</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33705</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33705</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33705</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36300</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36300</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36300</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66511</t>
+          <t>63568</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66511</t>
+          <t>63568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66511</t>
+          <t>63568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4216</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7135</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>46,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4873</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>49,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4934</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7542</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>53,93%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>82,42%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>8108</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>4890</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>9306</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>83,05%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>50,09%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>14155</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>16409</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,33%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>19700</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14017</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>26402</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>29,25%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>55,09%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>20332</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>13515</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>30398</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>42,21%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>63,11%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22327</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>34060</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54485</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>26827</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19354</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>32518</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>55,98%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>40,39%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>67,86%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>27179</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>16782</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>33783</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>56,43%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>70,14%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>56121</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>63492</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -2653,107 +2653,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>4720</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>5218</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>4832</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>618</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
